--- a/docs/test-results/staged-replay-20260929-r1.xlsx
+++ b/docs/test-results/staged-replay-20260929-r1.xlsx
@@ -282,7 +282,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">ふつうの返事で段階</t>
+      <t xml:space="preserve">自由な発言で段階</t>
     </r>
     <r>
       <rPr>
@@ -488,7 +488,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">ふつうの返事</t>
+      <t xml:space="preserve">ふつうの返事で段階が上がらないか</t>
     </r>
     <r>
       <rPr>
@@ -505,7 +505,75 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">生徒役の自由な発言で、キーワード・受動パターンを含まないもの</t>
+      <t xml:space="preserve">「自由な発言で段階</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以上」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">生徒役の自由な発言で、キーワード・受動パターンを含まないもののうち段階</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以上になった数。気がかりな発言</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「無理だしどうでもいい」等</t>
     </r>
     <r>
       <rPr>
@@ -522,24 +590,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">で段階が上がらないか</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">「ふつうの返事で段階</t>
+      <t xml:space="preserve">の段階</t>
     </r>
     <r>
       <rPr>
@@ -556,24 +607,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">以上」が </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Yu Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か</t>
+      <t xml:space="preserve">は正しい判定なので、どの発言かは「ターンごと」で見る</t>
     </r>
     <r>
       <rPr>
